--- a/library_management_system.xlsx
+++ b/library_management_system.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nakul Kalra\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Code\capegemini\testing\sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2762CAD-011F-410E-AAFE-7AB89E8A704E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4523354B-5576-45A9-A8C5-4419554C41D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -530,9 +530,6 @@
     <t>VERIFY THAT SUBMIT WORKS IN CASE OF INVALID FIELDS</t>
   </si>
   <si>
-    <t>Update User</t>
-  </si>
-  <si>
     <t>LM_UU_001</t>
   </si>
   <si>
@@ -857,9 +854,6 @@
     <t>VERIFY THAT CANCEL BUTTON NAVIGATES BACK TO USER LIST / DASHBOARD</t>
   </si>
   <si>
-    <t>User Login</t>
-  </si>
-  <si>
     <t>LM_UL_001</t>
   </si>
   <si>
@@ -1055,10 +1049,17 @@
     <t>VERIFY THAT 2 FAILED ATTEMPTS DO NOT LOCK THE ACCOUNT</t>
   </si>
   <si>
-    <t>ACCOUNT LOCK</t>
-  </si>
-  <si>
     <t>LOGIN BUTTON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACCOUNT LOCK
+</t>
+  </si>
+  <si>
+    <t>USER LOGIN</t>
+  </si>
+  <si>
+    <t>UPDATE USER</t>
   </si>
 </sst>
 </file>
@@ -1099,7 +1100,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1122,44 +1123,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1179,29 +1147,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1574,7 +1537,7 @@
       <c r="A8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="5" t="s">
@@ -1591,7 +1554,7 @@
       <c r="A9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="11"/>
+      <c r="B9" s="10"/>
       <c r="C9" s="5" t="s">
         <v>17</v>
       </c>
@@ -1606,7 +1569,7 @@
       <c r="A10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="11"/>
+      <c r="B10" s="10"/>
       <c r="C10" s="5" t="s">
         <v>21</v>
       </c>
@@ -1621,7 +1584,7 @@
       <c r="A11" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="11"/>
+      <c r="B11" s="10"/>
       <c r="C11" s="5" t="s">
         <v>23</v>
       </c>
@@ -1636,7 +1599,7 @@
       <c r="A12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="11"/>
+      <c r="B12" s="10"/>
       <c r="C12" s="5" t="s">
         <v>25</v>
       </c>
@@ -1651,7 +1614,7 @@
       <c r="A13" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="11"/>
+      <c r="B13" s="10"/>
       <c r="C13" s="5" t="s">
         <v>27</v>
       </c>
@@ -1666,7 +1629,7 @@
       <c r="A14" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="11"/>
+      <c r="B14" s="10"/>
       <c r="C14" s="5" t="s">
         <v>29</v>
       </c>
@@ -1681,7 +1644,7 @@
       <c r="A15" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="11"/>
+      <c r="B15" s="10"/>
       <c r="C15" s="5" t="s">
         <v>31</v>
       </c>
@@ -1696,7 +1659,7 @@
       <c r="A16" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="11"/>
+      <c r="B16" s="10"/>
       <c r="C16" s="5" t="s">
         <v>34</v>
       </c>
@@ -1711,7 +1674,7 @@
       <c r="A17" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="11"/>
+      <c r="B17" s="10"/>
       <c r="C17" s="5" t="s">
         <v>36</v>
       </c>
@@ -1726,7 +1689,7 @@
       <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="11"/>
+      <c r="B18" s="10"/>
       <c r="C18" s="5" t="s">
         <v>39</v>
       </c>
@@ -1741,7 +1704,7 @@
       <c r="A19" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="12"/>
+      <c r="B19" s="10"/>
       <c r="C19" s="5" t="s">
         <v>41</v>
       </c>
@@ -1756,7 +1719,7 @@
       <c r="A20" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="7" t="s">
         <v>43</v>
       </c>
       <c r="C20" s="5" t="s">
@@ -1773,7 +1736,7 @@
       <c r="A21" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="11"/>
+      <c r="B21" s="10"/>
       <c r="C21" s="5" t="s">
         <v>17</v>
       </c>
@@ -1788,7 +1751,7 @@
       <c r="A22" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="11"/>
+      <c r="B22" s="10"/>
       <c r="C22" s="5" t="s">
         <v>21</v>
       </c>
@@ -1803,7 +1766,7 @@
       <c r="A23" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="11"/>
+      <c r="B23" s="10"/>
       <c r="C23" s="5" t="s">
         <v>23</v>
       </c>
@@ -1818,7 +1781,7 @@
       <c r="A24" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="11"/>
+      <c r="B24" s="10"/>
       <c r="C24" s="5" t="s">
         <v>25</v>
       </c>
@@ -1833,7 +1796,7 @@
       <c r="A25" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="11"/>
+      <c r="B25" s="10"/>
       <c r="C25" s="5" t="s">
         <v>27</v>
       </c>
@@ -1848,7 +1811,7 @@
       <c r="A26" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="11"/>
+      <c r="B26" s="10"/>
       <c r="C26" s="5" t="s">
         <v>29</v>
       </c>
@@ -1863,7 +1826,7 @@
       <c r="A27" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="11"/>
+      <c r="B27" s="10"/>
       <c r="C27" s="5" t="s">
         <v>31</v>
       </c>
@@ -1878,7 +1841,7 @@
       <c r="A28" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B28" s="11"/>
+      <c r="B28" s="10"/>
       <c r="C28" s="5" t="s">
         <v>34</v>
       </c>
@@ -1893,7 +1856,7 @@
       <c r="A29" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B29" s="11"/>
+      <c r="B29" s="10"/>
       <c r="C29" s="5" t="s">
         <v>36</v>
       </c>
@@ -1908,7 +1871,7 @@
       <c r="A30" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B30" s="11"/>
+      <c r="B30" s="10"/>
       <c r="C30" s="5" t="s">
         <v>39</v>
       </c>
@@ -1923,7 +1886,7 @@
       <c r="A31" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B31" s="12"/>
+      <c r="B31" s="10"/>
       <c r="C31" s="5" t="s">
         <v>41</v>
       </c>
@@ -1938,7 +1901,7 @@
       <c r="A32" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="7" t="s">
         <v>56</v>
       </c>
       <c r="C32" s="5" t="s">
@@ -1955,7 +1918,7 @@
       <c r="A33" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="11"/>
+      <c r="B33" s="10"/>
       <c r="C33" s="5" t="s">
         <v>59</v>
       </c>
@@ -1970,7 +1933,7 @@
       <c r="A34" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B34" s="11"/>
+      <c r="B34" s="10"/>
       <c r="C34" s="5" t="s">
         <v>61</v>
       </c>
@@ -1985,7 +1948,7 @@
       <c r="A35" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B35" s="11"/>
+      <c r="B35" s="10"/>
       <c r="C35" s="5" t="s">
         <v>63</v>
       </c>
@@ -2000,7 +1963,7 @@
       <c r="A36" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B36" s="11"/>
+      <c r="B36" s="10"/>
       <c r="C36" s="5" t="s">
         <v>65</v>
       </c>
@@ -2015,7 +1978,7 @@
       <c r="A37" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B37" s="11"/>
+      <c r="B37" s="10"/>
       <c r="C37" s="5" t="s">
         <v>67</v>
       </c>
@@ -2030,7 +1993,7 @@
       <c r="A38" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B38" s="11"/>
+      <c r="B38" s="10"/>
       <c r="C38" s="5" t="s">
         <v>69</v>
       </c>
@@ -2045,7 +2008,7 @@
       <c r="A39" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B39" s="11"/>
+      <c r="B39" s="10"/>
       <c r="C39" s="5" t="s">
         <v>71</v>
       </c>
@@ -2060,7 +2023,7 @@
       <c r="A40" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B40" s="11"/>
+      <c r="B40" s="10"/>
       <c r="C40" s="5" t="s">
         <v>73</v>
       </c>
@@ -2075,7 +2038,7 @@
       <c r="A41" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B41" s="12"/>
+      <c r="B41" s="10"/>
       <c r="C41" s="5" t="s">
         <v>75</v>
       </c>
@@ -2090,7 +2053,7 @@
       <c r="A42" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B42" s="7" t="s">
         <v>77</v>
       </c>
       <c r="C42" s="5" t="s">
@@ -2107,7 +2070,7 @@
       <c r="A43" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B43" s="11"/>
+      <c r="B43" s="10"/>
       <c r="C43" s="5" t="s">
         <v>80</v>
       </c>
@@ -2122,7 +2085,7 @@
       <c r="A44" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B44" s="11"/>
+      <c r="B44" s="10"/>
       <c r="C44" s="5" t="s">
         <v>82</v>
       </c>
@@ -2137,7 +2100,7 @@
       <c r="A45" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B45" s="11"/>
+      <c r="B45" s="10"/>
       <c r="C45" s="5" t="s">
         <v>84</v>
       </c>
@@ -2152,7 +2115,7 @@
       <c r="A46" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B46" s="11"/>
+      <c r="B46" s="10"/>
       <c r="C46" s="5" t="s">
         <v>86</v>
       </c>
@@ -2167,7 +2130,7 @@
       <c r="A47" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B47" s="11"/>
+      <c r="B47" s="10"/>
       <c r="C47" s="5" t="s">
         <v>88</v>
       </c>
@@ -2182,7 +2145,7 @@
       <c r="A48" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B48" s="11"/>
+      <c r="B48" s="10"/>
       <c r="C48" s="5" t="s">
         <v>90</v>
       </c>
@@ -2197,7 +2160,7 @@
       <c r="A49" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B49" s="11"/>
+      <c r="B49" s="10"/>
       <c r="C49" s="5" t="s">
         <v>92</v>
       </c>
@@ -2212,7 +2175,7 @@
       <c r="A50" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B50" s="12"/>
+      <c r="B50" s="10"/>
       <c r="C50" s="5" t="s">
         <v>94</v>
       </c>
@@ -2227,7 +2190,7 @@
       <c r="A51" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B51" s="10" t="s">
+      <c r="B51" s="7" t="s">
         <v>96</v>
       </c>
       <c r="C51" s="5" t="s">
@@ -2244,7 +2207,7 @@
       <c r="A52" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B52" s="11"/>
+      <c r="B52" s="10"/>
       <c r="C52" s="5" t="s">
         <v>99</v>
       </c>
@@ -2259,7 +2222,7 @@
       <c r="A53" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B53" s="11"/>
+      <c r="B53" s="10"/>
       <c r="C53" s="5" t="s">
         <v>101</v>
       </c>
@@ -2274,7 +2237,7 @@
       <c r="A54" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B54" s="11"/>
+      <c r="B54" s="10"/>
       <c r="C54" s="5" t="s">
         <v>103</v>
       </c>
@@ -2289,7 +2252,7 @@
       <c r="A55" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B55" s="11"/>
+      <c r="B55" s="10"/>
       <c r="C55" s="5" t="s">
         <v>105</v>
       </c>
@@ -2304,7 +2267,7 @@
       <c r="A56" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B56" s="11"/>
+      <c r="B56" s="10"/>
       <c r="C56" s="5" t="s">
         <v>107</v>
       </c>
@@ -2319,7 +2282,7 @@
       <c r="A57" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B57" s="11"/>
+      <c r="B57" s="10"/>
       <c r="C57" s="5" t="s">
         <v>109</v>
       </c>
@@ -2334,7 +2297,7 @@
       <c r="A58" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B58" s="11"/>
+      <c r="B58" s="10"/>
       <c r="C58" s="5" t="s">
         <v>111</v>
       </c>
@@ -2349,7 +2312,7 @@
       <c r="A59" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B59" s="12"/>
+      <c r="B59" s="10"/>
       <c r="C59" s="5" t="s">
         <v>113</v>
       </c>
@@ -2364,16 +2327,16 @@
       <c r="A60" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B60" s="13" t="s">
+      <c r="B60" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="D60" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E60" s="4" t="s">
+      <c r="D60" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E60" s="12" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2381,11 +2344,11 @@
       <c r="A61" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B61" s="9"/>
-      <c r="C61" s="4" t="s">
+      <c r="B61" s="13"/>
+      <c r="C61" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="D61" s="12" t="s">
         <v>18</v>
       </c>
       <c r="E61" s="5" t="s">
@@ -2396,11 +2359,11 @@
       <c r="A62" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B62" s="9"/>
-      <c r="C62" s="4" t="s">
+      <c r="B62" s="13"/>
+      <c r="C62" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D62" s="12" t="s">
         <v>18</v>
       </c>
       <c r="E62" s="5" t="s">
@@ -2411,16 +2374,16 @@
       <c r="A63" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="B63" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="C63" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="D63" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E63" s="4" t="s">
+      <c r="D63" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63" s="12" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2428,14 +2391,14 @@
       <c r="A64" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B64" s="9"/>
-      <c r="C64" s="4" t="s">
+      <c r="B64" s="13"/>
+      <c r="C64" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D64" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E64" s="4" t="s">
+      <c r="D64" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64" s="12" t="s">
         <v>127</v>
       </c>
     </row>
@@ -2443,14 +2406,14 @@
       <c r="A65" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B65" s="9"/>
-      <c r="C65" s="4" t="s">
+      <c r="B65" s="13"/>
+      <c r="C65" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="D65" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E65" s="4" t="s">
+      <c r="D65" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E65" s="12" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2458,14 +2421,14 @@
       <c r="A66" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B66" s="9"/>
-      <c r="C66" s="4" t="s">
+      <c r="B66" s="13"/>
+      <c r="C66" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D66" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E66" s="4" t="s">
+      <c r="D66" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="12" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2473,14 +2436,14 @@
       <c r="A67" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B67" s="9"/>
-      <c r="C67" s="4" t="s">
+      <c r="B67" s="13"/>
+      <c r="C67" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="D67" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E67" s="4" t="s">
+      <c r="D67" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="12" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2488,14 +2451,14 @@
       <c r="A68" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B68" s="9"/>
-      <c r="C68" s="4" t="s">
+      <c r="B68" s="13"/>
+      <c r="C68" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="D68" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E68" s="4" t="s">
+      <c r="D68" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E68" s="12" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2503,14 +2466,14 @@
       <c r="A69" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="B69" s="9"/>
-      <c r="C69" s="4" t="s">
+      <c r="B69" s="13"/>
+      <c r="C69" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="D69" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E69" s="4" t="s">
+      <c r="D69" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E69" s="12" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2518,14 +2481,14 @@
       <c r="A70" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B70" s="9"/>
-      <c r="C70" s="4" t="s">
+      <c r="B70" s="13"/>
+      <c r="C70" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="D70" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E70" s="4" t="s">
+      <c r="D70" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E70" s="12" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2533,11 +2496,11 @@
       <c r="A71" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B71" s="9"/>
-      <c r="C71" s="4" t="s">
+      <c r="B71" s="13"/>
+      <c r="C71" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="D71" s="12" t="s">
         <v>18</v>
       </c>
       <c r="E71" s="5" t="s">
@@ -2548,16 +2511,16 @@
       <c r="A72" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="C72" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="D72" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E72" s="4" t="s">
+      <c r="D72" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E72" s="12" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2565,14 +2528,14 @@
       <c r="A73" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B73" s="9"/>
-      <c r="C73" s="4" t="s">
+      <c r="B73" s="13"/>
+      <c r="C73" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="D73" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E73" s="4" t="s">
+      <c r="D73" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E73" s="12" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2580,11 +2543,11 @@
       <c r="A74" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B74" s="9"/>
-      <c r="C74" s="4" t="s">
+      <c r="B74" s="13"/>
+      <c r="C74" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="D74" s="12" t="s">
         <v>18</v>
       </c>
       <c r="E74" s="5" t="s">
@@ -2595,16 +2558,16 @@
       <c r="A75" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="B75" s="8" t="s">
+      <c r="B75" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="C75" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="D75" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E75" s="4" t="s">
+      <c r="D75" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E75" s="12" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2612,11 +2575,11 @@
       <c r="A76" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B76" s="9"/>
-      <c r="C76" s="4" t="s">
+      <c r="B76" s="13"/>
+      <c r="C76" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="D76" s="4" t="s">
+      <c r="D76" s="12" t="s">
         <v>18</v>
       </c>
       <c r="E76" s="5" t="s">
@@ -2627,16 +2590,16 @@
       <c r="A77" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="B77" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="C77" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="D77" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E77" s="4" t="s">
+      <c r="D77" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E77" s="12" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2644,14 +2607,14 @@
       <c r="A78" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B78" s="9"/>
-      <c r="C78" s="4" t="s">
+      <c r="B78" s="13"/>
+      <c r="C78" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="D78" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E78" s="4" t="s">
+      <c r="D78" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E78" s="12" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2659,14 +2622,14 @@
       <c r="A79" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B79" s="9"/>
-      <c r="C79" s="4" t="s">
+      <c r="B79" s="13"/>
+      <c r="C79" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="D79" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E79" s="4" t="s">
+      <c r="D79" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E79" s="12" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2674,14 +2637,14 @@
       <c r="A80" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B80" s="9"/>
-      <c r="C80" s="4" t="s">
+      <c r="B80" s="13"/>
+      <c r="C80" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="D80" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E80" s="4" t="s">
+      <c r="D80" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E80" s="12" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2689,14 +2652,14 @@
       <c r="A81" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B81" s="9"/>
-      <c r="C81" s="4" t="s">
+      <c r="B81" s="13"/>
+      <c r="C81" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="D81" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E81" s="4" t="s">
+      <c r="D81" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E81" s="12" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2704,11 +2667,11 @@
       <c r="A82" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="B82" s="9"/>
-      <c r="C82" s="4" t="s">
+      <c r="B82" s="13"/>
+      <c r="C82" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="D82" s="4" t="s">
+      <c r="D82" s="12" t="s">
         <v>18</v>
       </c>
       <c r="E82" s="5" t="s">
@@ -2717,16 +2680,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B75:B76"/>
+    <mergeCell ref="B51:B59"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="B77:B82"/>
+    <mergeCell ref="B42:B50"/>
     <mergeCell ref="B8:B19"/>
     <mergeCell ref="B60:B62"/>
     <mergeCell ref="B20:B31"/>
     <mergeCell ref="B63:B71"/>
     <mergeCell ref="B32:B41"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="B51:B59"/>
-    <mergeCell ref="B72:B74"/>
-    <mergeCell ref="B77:B82"/>
-    <mergeCell ref="B42:B50"/>
   </mergeCells>
   <conditionalFormatting sqref="A8:E59 A60:A82">
     <cfRule type="dataBar" priority="7">
@@ -2821,7 +2784,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>167</v>
+        <v>343</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2850,788 +2813,789 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="C6" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="7" t="s">
+      <c r="B7" s="10"/>
+      <c r="C7" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B9" s="10"/>
+      <c r="C9" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B10" s="10"/>
+      <c r="C10" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="7" t="s">
+    <row r="15" spans="1:5">
+      <c r="A15" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="B16" s="10"/>
+      <c r="C16" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="B17" s="10"/>
+      <c r="C17" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="B18" s="10"/>
+      <c r="C18" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="B19" s="10"/>
+      <c r="C19" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="7" t="s">
+    <row r="20" spans="1:5">
+      <c r="A20" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="B20" s="10"/>
+      <c r="C20" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="7" t="s">
+    <row r="21" spans="1:5">
+      <c r="A21" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="B21" s="10"/>
+      <c r="C21" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="7" t="s">
+    <row r="22" spans="1:5">
+      <c r="A22" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="7" t="s">
+    <row r="23" spans="1:5">
+      <c r="A23" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="B23" s="10"/>
+      <c r="C23" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="B24" s="10"/>
+      <c r="C24" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B25" s="10"/>
+      <c r="C25" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="B26" s="10"/>
+      <c r="C26" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="B27" s="10"/>
+      <c r="C27" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="B28" s="10"/>
+      <c r="C28" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="7" t="s">
+    <row r="30" spans="1:5">
+      <c r="A30" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="B30" s="10"/>
+      <c r="C30" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B31" s="10"/>
+      <c r="C31" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B32" s="10"/>
+      <c r="C32" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B33" s="10"/>
+      <c r="C33" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="B34" s="10"/>
+      <c r="C34" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B36" s="10"/>
+      <c r="C36" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="B37" s="10"/>
+      <c r="C37" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="B38" s="10"/>
+      <c r="C38" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="B39" s="10"/>
+      <c r="C39" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" s="7" t="s">
+    <row r="40" spans="1:5">
+      <c r="A40" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="B40" s="10"/>
+      <c r="C40" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="7" t="s">
+    <row r="41" spans="1:5">
+      <c r="A41" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="7" t="s">
+    <row r="42" spans="1:5">
+      <c r="A42" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="B42" s="10"/>
+      <c r="C42" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="B32" s="15"/>
-      <c r="C32" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="B34" s="15"/>
-      <c r="C34" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E34" s="7" t="s">
+    <row r="43" spans="1:5">
+      <c r="A43" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="B43" s="10"/>
+      <c r="C43" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E44" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" s="7" t="s">
+    <row r="45" spans="1:5">
+      <c r="A45" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="B45" s="10"/>
+      <c r="C45" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E45" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="B36" s="15"/>
-      <c r="C36" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="B37" s="15"/>
-      <c r="C37" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="B39" s="15"/>
-      <c r="C39" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="B40" s="15"/>
-      <c r="C40" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="B41" s="14" t="s">
-        <v>242</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E41" s="7" t="s">
+    <row r="46" spans="1:5">
+      <c r="A46" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="B46" s="10"/>
+      <c r="C46" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E47" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="B42" s="15"/>
-      <c r="C42" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E42" s="7" t="s">
+    <row r="48" spans="1:5">
+      <c r="A48" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="B48" s="9"/>
+      <c r="C48" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E48" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="B43" s="15"/>
-      <c r="C43" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="B44" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E44" s="7" t="s">
+    <row r="49" spans="1:5">
+      <c r="A49" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="B49" s="9"/>
+      <c r="C49" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E49" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="B45" s="15"/>
-      <c r="C45" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E45" s="7" t="s">
+    <row r="50" spans="1:5">
+      <c r="A50" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="B50" s="9"/>
+      <c r="C50" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="B51" s="9"/>
+      <c r="C51" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="B52" s="9"/>
+      <c r="C52" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="B53" s="9"/>
+      <c r="C53" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="B54" s="9"/>
+      <c r="C54" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="B55" s="9"/>
+      <c r="C55" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E55" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="B46" s="15"/>
-      <c r="C46" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="B47" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="B48" s="14"/>
-      <c r="C48" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="B49" s="14"/>
-      <c r="C49" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="B50" s="14"/>
-      <c r="C50" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="B51" s="14"/>
-      <c r="C51" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="B52" s="14"/>
-      <c r="C52" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="B53" s="14"/>
-      <c r="C53" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="B54" s="14"/>
-      <c r="C54" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="B55" s="14"/>
-      <c r="C55" s="7" t="s">
+    <row r="56" spans="1:5">
+      <c r="A56" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="D55" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="7" t="s">
+      <c r="B56" s="9"/>
+      <c r="C56" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="B56" s="14"/>
-      <c r="C56" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E56" s="7" t="s">
+      <c r="D56" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E56" s="8" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="B6:B14"/>
     <mergeCell ref="B41:B43"/>
     <mergeCell ref="B29:B34"/>
     <mergeCell ref="B15:B21"/>
@@ -3639,7 +3603,6 @@
     <mergeCell ref="B35:B40"/>
     <mergeCell ref="B22:B28"/>
     <mergeCell ref="B44:B46"/>
-    <mergeCell ref="B6:B14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3670,7 +3633,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>276</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3699,514 +3662,514 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="B7" s="10"/>
+      <c r="C7" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="7" t="s">
+      <c r="D7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="B9" s="10"/>
+      <c r="C9" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="B10" s="10"/>
+      <c r="C10" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="7" t="s">
+    <row r="15" spans="1:5">
+      <c r="A15" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="7" t="s">
+    <row r="17" spans="1:5">
+      <c r="A17" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="7" t="s">
+    <row r="18" spans="1:5">
+      <c r="A18" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="B19" s="9"/>
+      <c r="C19" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="B20" s="9"/>
+      <c r="C20" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="7" t="s">
+    <row r="21" spans="1:5">
+      <c r="A21" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="B22" s="9"/>
+      <c r="C22" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="B23" s="9"/>
+      <c r="C23" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="B24" s="9"/>
+      <c r="C24" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="B33" s="7"/>
+      <c r="C33" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="7" t="s">
+    <row r="34" spans="1:5">
+      <c r="A34" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="B34" s="7"/>
+      <c r="C34" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="B35" s="7"/>
+      <c r="C35" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="B36" s="7"/>
+      <c r="C36" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="7" t="s">
+    <row r="37" spans="1:5">
+      <c r="A37" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="B37" s="7"/>
+      <c r="C37" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>343</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>342</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="B32" s="15"/>
-      <c r="C32" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="B34" s="15"/>
-      <c r="C34" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="B35" s="15"/>
-      <c r="C35" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="B36" s="15"/>
-      <c r="C36" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="7" t="s">
+    <row r="38" spans="1:5">
+      <c r="A38" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="B37" s="15"/>
-      <c r="C37" s="7" t="s">
+      <c r="B38" s="7"/>
+      <c r="C38" s="8" t="s">
         <v>339</v>
       </c>
-      <c r="D37" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E38" s="7" t="s">
+      <c r="D38" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" s="8" t="s">
         <v>37</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B30:B38"/>
     <mergeCell ref="B6:B13"/>
-    <mergeCell ref="B14:B23"/>
-    <mergeCell ref="B24:B29"/>
+    <mergeCell ref="B14:B25"/>
+    <mergeCell ref="B26:B31"/>
+    <mergeCell ref="B32:B38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
